--- a/samples/가상_실양식_급여테이블.xlsx
+++ b/samples/가상_실양식_급여테이블.xlsx
@@ -10,6 +10,8 @@
   <sheets>
     <sheet name="급여테이블(변경전)" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="급여테이블(변경후)" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="견적서" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="견적대비 비교" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="164">
   <si>
     <r>
       <rPr>
@@ -1829,6 +1831,592 @@
       </rPr>
       <t xml:space="preserve">강사</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○ 센터명 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○ 계약기간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026.01.01. ~ 2026.12.31.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">팀장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">일반상담</t>
+  </si>
+  <si>
+    <t xml:space="preserve">심야상담</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">산출근거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인원 ①</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계약 정원 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인건비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직접 인건비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">초과수당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연차수당</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교통비</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직책</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전문수당</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성과급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인센티브</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">휴일근로수당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직접인건비 소계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실비 청구 항목 등 표기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">간접 인건비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">퇴직충당금</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)/12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">간접인건비 소계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일반관리비 ③ 값 반영⇒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기업이윤 ④   값 반영⇒</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총합계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(vat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">급여테이블 견적 대사</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">* ERP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상 직접비 총계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직전년도연간 인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">급여 테이블</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직접비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직접비 총계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">호봉별 총원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">통상임금</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">초과근로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">야근수당</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">소계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">견적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직접비 단가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직무별 직접비 계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월 보수 가용 범위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap</t>
   </si>
 </sst>
 </file>
@@ -6868,4 +7456,1051 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:J40"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J4" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <f aca="false">SUM(E6:H6)</f>
+        <v>24</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E7:H7,$E$6:$H$6)</f>
+        <v>51840000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E8:H8,$E$6:$H$6)</f>
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E9:H9,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E10:H10,$E$6:$H$6)</f>
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E11:H11,$E$6:$H$6)</f>
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E12:H12,$E$6:$H$6)</f>
+        <v>1650000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E13:H13,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <f aca="false">SUM(E7:E13)</f>
+        <v>3290000</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>2810000</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <f aca="false">SUM(G7:G13)</f>
+        <v>2410000</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <f aca="false">SUM(H7:H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E14:H14,$E$6:$H$6)</f>
+        <v>59920000</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <f aca="false">ROUND(E14/12,0)</f>
+        <v>274167</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <f aca="false">ROUND(F14/12,0)</f>
+        <v>234167</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <f aca="false">ROUND(G14/12,0)</f>
+        <v>200833</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:Y24"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <f aca="false">SUM(L7:Y7)</f>
+        <v>24</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q72</f>
+        <v>3036880</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D72</f>
+        <v>2656880</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E72</f>
+        <v>2536880</v>
+      </c>
+      <c r="R8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D41</f>
+        <v>2256880</v>
+      </c>
+      <c r="T8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E41</f>
+        <v>2256880</v>
+      </c>
+      <c r="V8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F41</f>
+        <v>2276880</v>
+      </c>
+      <c r="X8" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G41</f>
+        <v>2296880</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q79</f>
+        <v>108980</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D79</f>
+        <v>95350</v>
+      </c>
+      <c r="P11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E79</f>
+        <v>91040</v>
+      </c>
+      <c r="R11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D48</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E48</f>
+        <v>32400</v>
+      </c>
+      <c r="V11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F48</f>
+        <v>32690</v>
+      </c>
+      <c r="X11" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G48</f>
+        <v>32970</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <f aca="false">SUM(L12:Y12)</f>
+        <v>57210090</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">SUM(L8:M11)*L7</f>
+        <v>3145860</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <f aca="false">SUM(N8:O11)*N7</f>
+        <v>5504460</v>
+      </c>
+      <c r="P12" s="0" t="n">
+        <f aca="false">SUM(P8:Q11)*P7</f>
+        <v>2627920</v>
+      </c>
+      <c r="R12" s="0" t="n">
+        <f aca="false">SUM(R8:S11)*R7</f>
+        <v>6770640</v>
+      </c>
+      <c r="T12" s="0" t="n">
+        <f aca="false">SUM(T8:U11)*T7</f>
+        <v>18314240</v>
+      </c>
+      <c r="V12" s="0" t="n">
+        <f aca="false">SUM(V8:W11)*V7</f>
+        <v>13857420</v>
+      </c>
+      <c r="X12" s="0" t="n">
+        <f aca="false">SUM(X8:Y11)*X7</f>
+        <v>6989550</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K14" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q73</f>
+        <v>200000</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D73</f>
+        <v>200000</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E73</f>
+        <v>200000</v>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D42</f>
+        <v>120000</v>
+      </c>
+      <c r="S14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E42</f>
+        <v>120000</v>
+      </c>
+      <c r="U14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F42</f>
+        <v>120000</v>
+      </c>
+      <c r="W14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G42</f>
+        <v>120000</v>
+      </c>
+      <c r="Y14" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K15" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q74</f>
+        <v>150000</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D74</f>
+        <v>150000</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E74</f>
+        <v>150000</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D43</f>
+        <v>90000</v>
+      </c>
+      <c r="S15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E43</f>
+        <v>90000</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F43</f>
+        <v>90000</v>
+      </c>
+      <c r="W15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G43</f>
+        <v>90000</v>
+      </c>
+      <c r="Y15" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K16" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q75</f>
+        <v>100000</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D75</f>
+        <v>100000</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E75</f>
+        <v>100000</v>
+      </c>
+      <c r="Q16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D44</f>
+        <v>60000</v>
+      </c>
+      <c r="S16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E44</f>
+        <v>60000</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F44</f>
+        <v>60000</v>
+      </c>
+      <c r="W16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G44</f>
+        <v>60000</v>
+      </c>
+      <c r="Y16" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q76</f>
+        <v>50000</v>
+      </c>
+      <c r="M17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D76</f>
+        <v>50000</v>
+      </c>
+      <c r="O17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E76</f>
+        <v>50000</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D45</f>
+        <v>30000</v>
+      </c>
+      <c r="S17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E45</f>
+        <v>30000</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F45</f>
+        <v>30000</v>
+      </c>
+      <c r="W17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G45</f>
+        <v>30000</v>
+      </c>
+      <c r="Y17" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q77</f>
+        <v>20000</v>
+      </c>
+      <c r="M18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D77</f>
+        <v>20000</v>
+      </c>
+      <c r="O18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E77</f>
+        <v>20000</v>
+      </c>
+      <c r="Q18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D46</f>
+        <v>10000</v>
+      </c>
+      <c r="S18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E46</f>
+        <v>10000</v>
+      </c>
+      <c r="U18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F46</f>
+        <v>10000</v>
+      </c>
+      <c r="W18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G46</f>
+        <v>10000</v>
+      </c>
+      <c r="Y18" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!Q78</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D78</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E78</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!D47</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!E47</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!F47</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="0" t="n">
+        <f aca="false">'급여테이블(변경후)'!G47</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <f aca="false">SUM(D20:G20)</f>
+        <v>24</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <f aca="false">견적서!E14</f>
+        <v>3290000</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <f aca="false">견적서!F14</f>
+        <v>2810000</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <f aca="false">견적서!G14</f>
+        <v>2410000</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <f aca="false">견적서!H14</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(L14:L20,M14:M20)</f>
+        <v>150000</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(N14:N20,O14:O20)</f>
+        <v>250000</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(P14:P20,Q14:Q20)</f>
+        <v>100000</v>
+      </c>
+      <c r="R21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(R14:R20,S14:S20)</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(T14:T20,U14:U20)</f>
+        <v>520000</v>
+      </c>
+      <c r="V21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(V14:V20,W14:W20)</f>
+        <v>420000</v>
+      </c>
+      <c r="X21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(X14:X20,Y14:Y20)</f>
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <f aca="false">D20*D21</f>
+        <v>3290000</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <f aca="false">E20*E21</f>
+        <v>8430000</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <f aca="false">F20*F21</f>
+        <v>48200000</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <f aca="false">G20*G21</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <f aca="false">SUM(D22:G22)</f>
+        <v>59920000</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <f aca="false">SUM(L22:Y22)</f>
+        <v>58860090</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <f aca="false">L12+L21</f>
+        <v>3295860</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <f aca="false">N12+N21</f>
+        <v>5754460</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <f aca="false">P12+P21</f>
+        <v>2727920</v>
+      </c>
+      <c r="R22" s="0" t="n">
+        <f aca="false">R12+R21</f>
+        <v>6770640</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <f aca="false">T12+T21</f>
+        <v>18834240</v>
+      </c>
+      <c r="V22" s="0" t="n">
+        <f aca="false">V12+V21</f>
+        <v>14277420</v>
+      </c>
+      <c r="X22" s="0" t="n">
+        <f aca="false">X12+X21</f>
+        <v>7199550</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <f aca="false">1-F7</f>
+        <v>0.97</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <f aca="false">H22*G23</f>
+        <v>58122400</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <f aca="false">H23-K22</f>
+        <v>-737690</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/samples/가상_실양식_급여테이블.xlsx
+++ b/samples/가상_실양식_급여테이블.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="179">
   <si>
     <r>
       <rPr>
@@ -2168,13 +2168,198 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">국민연금</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)×4.5%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">건강보험</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)×3.545%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">장기요양보험</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)×0.46%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">고용보험</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)×1.15%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">산재보험</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접인건비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)×0.7%</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">간접인건비 소계</t>
   </si>
   <si>
+    <t xml:space="preserve">경비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">복리후생비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경비 소계</t>
+  </si>
+  <si>
     <t xml:space="preserve">일반관리비 ③ 값 반영⇒</t>
   </si>
   <si>
     <t xml:space="preserve">기업이윤 ④   값 반영⇒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가가치세</t>
   </si>
   <si>
     <r>
@@ -7698,16 +7883,234 @@
         <f aca="false">ROUND(G14/12,0)</f>
         <v>200833</v>
       </c>
+      <c r="I15" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E15:H15,$E$6:$H$6)</f>
+        <v>4993328</v>
+      </c>
       <c r="J15" s="0" t="s">
         <v>138</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <f aca="false">ROUND(E$14*0.045,0)</f>
+        <v>148050</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <f aca="false">ROUND(F$14*0.045,0)</f>
+        <v>126450</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <f aca="false">ROUND(G$14*0.045,0)</f>
+        <v>108450</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E16:H16,$E$6:$H$6)</f>
+        <v>2696400</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <f aca="false">ROUND(E$14*0.03545,0)</f>
+        <v>116631</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <f aca="false">ROUND(F$14*0.03545,0)</f>
+        <v>99615</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <f aca="false">ROUND(G$14*0.03545,0)</f>
+        <v>85435</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E17:H17,$E$6:$H$6)</f>
+        <v>2124176</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <f aca="false">ROUND(E$14*0.0046,0)</f>
+        <v>15134</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <f aca="false">ROUND(F$14*0.0046,0)</f>
+        <v>12926</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <f aca="false">ROUND(G$14*0.0046,0)</f>
+        <v>11086</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E18:H18,$E$6:$H$6)</f>
+        <v>275632</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <f aca="false">ROUND(E$14*0.0115,0)</f>
+        <v>37835</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <f aca="false">ROUND(F$14*0.0115,0)</f>
+        <v>32315</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <f aca="false">ROUND(G$14*0.0115,0)</f>
+        <v>27715</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E19:H19,$E$6:$H$6)</f>
+        <v>689080</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <f aca="false">ROUND(E$14*0.007,0)</f>
+        <v>23030</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <f aca="false">ROUND(F$14*0.007,0)</f>
+        <v>19670</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <f aca="false">ROUND(G$14*0.007,0)</f>
+        <v>16870</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E20:H20,$E$6:$H$6)</f>
+        <v>419440</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E21:H21,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E22:H22,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E23:H23,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E24:H24,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E25:H25,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <f aca="false">SUM(E15:E25)</f>
+        <v>614847</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <f aca="false">SUM(F15:F25)</f>
+        <v>525143</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <f aca="false">SUM(G15:G25)</f>
+        <v>450389</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E26:H26,$E$6:$H$6)</f>
+        <v>11198056</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E27:H27,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E28:H28,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E29:H29,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E30:H30,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E31:H31,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E32:H32,$E$6:$H$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E33:H33,$E$6:$H$6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D34" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="E34" s="0" t="n">
         <v>30000</v>
       </c>
@@ -7717,20 +8120,141 @@
       <c r="G34" s="0" t="n">
         <v>30000</v>
       </c>
+      <c r="I34" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E34:H34,$E$6:$H$6)</f>
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <f aca="false">SUM(E27:E34)</f>
+        <v>30000</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <f aca="false">SUM(F27:F34)</f>
+        <v>30000</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <f aca="false">SUM(G27:G34)</f>
+        <v>30000</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E35:H35,$E$6:$H$6)</f>
+        <v>720000</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <f aca="false">ROUND((E14+E26+E35)*$D$36,0)</f>
+        <v>196742</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <f aca="false">ROUND((F14+F26+F35)*$D$36,0)</f>
+        <v>168257</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <f aca="false">ROUND((G14+G26+G35)*$D$36,0)</f>
+        <v>144519</v>
+      </c>
+      <c r="I36" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E36:H36,$E$6:$H$6)</f>
+        <v>3591893</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <f aca="false">ROUND((E14+E26+E35+E36)*$D$37,0)</f>
+        <v>206579</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <f aca="false">ROUND((F14+F26+F35+F36)*$D$37,0)</f>
+        <v>176670</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <f aca="false">ROUND((G14+G26+G35+G36)*$D$37,0)</f>
+        <v>151745</v>
+      </c>
+      <c r="I37" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E37:H37,$E$6:$H$6)</f>
+        <v>3771489</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <f aca="false">E14+E26+E35+E36+E37</f>
+        <v>4338168</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <f aca="false">F14+F26+F35+F36+F37</f>
+        <v>3710070</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <f aca="false">G14+G26+G35+G36+G37</f>
+        <v>3186653</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E38:H38,$E$6:$H$6)</f>
+        <v>79201438</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <f aca="false">ROUND(E38*0.1,0)</f>
+        <v>433817</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <f aca="false">ROUND(F38*0.1,0)</f>
+        <v>371007</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <f aca="false">ROUND(G38*0.1,0)</f>
+        <v>318665</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E39:H39,$E$6:$H$6)</f>
+        <v>7920138</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
-        <v>142</v>
+        <v>157</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <f aca="false">E38+E39</f>
+        <v>4771985</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <f aca="false">F38+F39</f>
+        <v>4081077</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <f aca="false">G38+G39</f>
+        <v>3505318</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <f aca="false">SUMPRODUCT(E40:H40,$E$6:$H$6)</f>
+        <v>87121576</v>
       </c>
     </row>
   </sheetData>
@@ -7754,20 +8278,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="0" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7798,16 +8322,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.03</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="K7" s="0" t="n">
         <f aca="false">SUM(L7:Y7)</f>
@@ -7837,7 +8361,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J8" s="1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="L8" s="0" t="n">
         <f aca="false">'급여테이블(변경후)'!Q72</f>
@@ -7870,7 +8394,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J11" s="1" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">'급여테이블(변경후)'!Q79</f>
@@ -7903,7 +8427,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J12" s="1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="K12" s="0" t="n">
         <f aca="false">SUM(L12:Y12)</f>
@@ -7943,49 +8467,49 @@
         <v>63</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8152,10 +8676,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L17" s="0" t="n">
         <f aca="false">'급여테이블(변경후)'!Q76</f>
@@ -8212,7 +8736,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K18" s="0" t="s">
         <v>69</v>
@@ -8269,7 +8793,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>27</v>
@@ -8341,7 +8865,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1</v>
@@ -8357,12 +8881,12 @@
         <v>24</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D21" s="0" t="n">
         <f aca="false">견적서!E14</f>
@@ -8414,7 +8938,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D22" s="0" t="n">
         <f aca="false">D20*D21</f>
@@ -8474,7 +8998,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="G23" s="0" t="n">
         <f aca="false">1-F7</f>
@@ -8487,7 +9011,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="0" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="H24" s="0" t="n">
         <f aca="false">H23-K22</f>
